--- a/Frasers - SS 2026 Map Databook.xlsx
+++ b/Frasers - SS 2026 Map Databook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53f9fa3a01670801/Documents/GitHub/Python_Maps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{85DFC8B9-DF41-45C6-9DB7-4EC1DD367EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7CA56F3-1D07-4F34-9235-C90BFB258ECC}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{85DFC8B9-DF41-45C6-9DB7-4EC1DD367EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51A2002C-CE50-496B-B0EA-5E002D62047E}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{ABD751BA-5ACE-4369-BF7B-8031843F00E0}"/>
+    <workbookView minimized="1" xWindow="16695" yWindow="2595" windowWidth="18330" windowHeight="11370" activeTab="2" xr2:uid="{ABD751BA-5ACE-4369-BF7B-8031843F00E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Demo Audiences" sheetId="1" r:id="rId1"/>
@@ -2409,7 +2409,7 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3251,12 +3251,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="66acd3af-7794-401b-98b9-9ce8c3420f0f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3505,17 +3504,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="66acd3af-7794-401b-98b9-9ce8c3420f0f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F96DB9D-6A01-488E-B6FB-F9DA2EF722F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC45E5A9-534E-497C-B82C-940622362B12}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="66acd3af-7794-401b-98b9-9ce8c3420f0f"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7db8ff51-e79e-4e92-8966-503b87c271be"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3540,18 +3549,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC45E5A9-534E-497C-B82C-940622362B12}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F96DB9D-6A01-488E-B6FB-F9DA2EF722F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="66acd3af-7794-401b-98b9-9ce8c3420f0f"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7db8ff51-e79e-4e92-8966-503b87c271be"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>